--- a/POTAL_D12_Marketing_Partnerships.xlsx
+++ b/POTAL_D12_Marketing_Partnerships.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reddit" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instagram" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO Blog" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="채널 TODO" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파트너십" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D12 Dashboard" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW18 콜드이메일" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="LinkedIn" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Reddit" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Instagram" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="SEO Blog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="채널 TODO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="파트너십" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="D12 Dashboard" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="CW18 콜드이메일" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +55,9 @@
     </font>
     <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="10">
@@ -123,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -151,6 +155,7 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -516,6 +521,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>시간</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>v3 파이프라인 100%</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>마케팅 메시지에 '100% rule-based, 0 AI calls' 사용 가능</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>경쟁사 대비 차별화 포인트</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>21개 Section 전체 커버</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>미술품/무기/귀금속 등 전 산업 분류 가능</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>셀러 타겟 범위 확대</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-28 23:30 KST</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>외장하드 데이터 100% 검증</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>데이터 완전성 증명 → 마케팅 신뢰도 근거</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>콜드이메일/파트너십 근거 자료</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -679,7 +792,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -810,7 +923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -903,7 +1016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1003,7 +1116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1225,7 +1338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1331,7 +1444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1588,12 +1701,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
@@ -1628,7 +1735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/POTAL_D12_Marketing_Partnerships.xlsx
+++ b/POTAL_D12_Marketing_Partnerships.xlsx
@@ -7,15 +7,16 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CW21_20260328" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="LinkedIn" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Reddit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Instagram" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SEO Blog" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="채널 TODO" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="파트너십" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="D12 Dashboard" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CW18 콜드이메일" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CW22B_FreeBanner" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CW21_20260328" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LinkedIn" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Reddit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Instagram" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SEO Blog" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="채널 TODO" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="파트너십" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="D12 Dashboard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="CW18 콜드이메일" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,6 +522,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-29 21:20 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>변경사항</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FreeBanner 제거 (app/page.tsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>이유</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>히어로 '140 Features. All Free. Forever.'와 중복 메시지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>홈 화면 현재 상태</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>히어로에 무료 메시지 포함, 별도 배너 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>상세</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>콜드이메일 콘텐츠</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>cold-email-final.md EN/KR 업데이트: 100% HS정확도, 592 GRI규칙, 비용비교 강화</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>비교차트 수정</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>comparison-chart.html: 허위 사용자수 문구 제거, 정확한 기술 비교 문구로 교체</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Gmail 드래프트 67건</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>크로스보더 67사 개인화 콜드이메일 드래프트 생성 (US 46, UK 11, CA 6, IN 5, SG 3)</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>PH 에셋 확인</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Hero 1270×760 + Gallery 4장 + thumbnail 240×240 기존 완료 확인</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>글로벌 캠페인 이메일 검증</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CN 84/100 검증 완료. UK~UAE 터미널2 자동 진행 중. 기존 미검증 드래프트→반송 201건</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>⏳진행중</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -623,7 +875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -792,7 +1044,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -923,7 +1175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1016,7 +1268,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1116,7 +1368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1338,7 +1590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1444,7 +1696,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1733,177 +1985,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>순번</t>
-        </is>
-      </c>
-      <c r="B1" s="10" t="inlineStr">
-        <is>
-          <t>날짜</t>
-        </is>
-      </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>활동</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
-        <is>
-          <t>상세</t>
-        </is>
-      </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C2" s="11" t="inlineStr">
-        <is>
-          <t>콜드이메일 콘텐츠</t>
-        </is>
-      </c>
-      <c r="D2" s="11" t="inlineStr">
-        <is>
-          <t>cold-email-final.md EN/KR 업데이트: 100% HS정확도, 592 GRI규칙, 비용비교 강화</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>비교차트 수정</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>comparison-chart.html: 허위 사용자수 문구 제거, 정확한 기술 비교 문구로 교체</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Gmail 드래프트 67건</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>크로스보더 67사 개인화 콜드이메일 드래프트 생성 (US 46, UK 11, CA 6, IN 5, SG 3)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>PH 에셋 확인</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hero 1270×760 + Gallery 4장 + thumbnail 240×240 기존 완료 확인</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>글로벌 캠페인 이메일 검증</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CN 84/100 검증 완료. UK~UAE 터미널2 자동 진행 중. 기존 미검증 드래프트→반송 201건</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>⏳진행중</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/POTAL_D12_Marketing_Partnerships.xlsx
+++ b/POTAL_D12_Marketing_Partnerships.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CW22B_FreeBanner" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CW21_20260328" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="LinkedIn" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Reddit" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Instagram" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SEO Blog" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="채널 TODO" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="파트너십" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="D12 Dashboard" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="CW18 콜드이메일" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW22D_Marketplace" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW22B_FreeBanner" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW21_20260328" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LinkedIn" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reddit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instagram" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEO Blog" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="채널 TODO" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="파트너십" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D12 Dashboard" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CW18 콜드이메일" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +60,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="10">
@@ -128,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -157,6 +162,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -522,20 +528,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>내용</t>
         </is>
@@ -549,43 +555,159 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-29 21:20 KST</t>
+          <t>2026-03-30 KST</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>변경사항</t>
+          <t>작업</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FreeBanner 제거 (app/page.tsx)</t>
+          <t>SDK 배포 + 이커머스 마켓플레이스 4종 등록 추진</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>이유</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>히어로 '140 Features. All Free. Forever.'와 중복 메시지</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>홈 화면 현재 상태</t>
+          <t>[SDK]npm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>히어로에 무료 메시지 포함, 별도 배너 없음</t>
+          <t>potal-sdk@1.1.0 ✅ 배포 완료 → https://www.npmjs.com/package/potal-sdk</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>[SDK]PyPI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>potal@1.1.0 ✅ 배포 완료 → https://pypi.org/project/potal/1.1.0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>[마켓]WooCommerce</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>✅ WordPress.org 제출 완료 (2026-03-30) — slug: potal-total-landed-cost-calculator</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>WooCommerce_상태</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Awaiting Review (826개 대기, 1~10일 소요) — soulmaten7@gmail.com으로 알림</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>WooCommerce_수정</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Plugin URI 분리, Tested up to 6.9, Stable tag 1.0.0, Text Domain 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>[마켓]BigCommerce</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>⏳ 파트너팀 이메일 발송 — partners@bigcommerce.com (답장 대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BigCommerce_이슈</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>자동 가입 불가: Gmail + business email 둘 다 차단됨</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>[마켓]Shopify</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>✅ Partners 설정 완료 (2026-03-29) — 심사 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>[마켓]Magento</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>⏳ Adobe Commerce Marketplace 제출 아직 안 함</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>다음우선순위</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1) BigCommerce 답장 확인 2) WooCommerce 심사 결과 3) Magento 제출 4) F045-F048 coming_soon 처리</t>
         </is>
       </c>
     </row>
@@ -595,6 +717,297 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>채널</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>게시물수</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>팔로워/구독자</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>트래픽</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>마지막업데이트</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PH 런치 포스트 + 첫 포스트 (2건)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Reddit</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>r/ecommerce 6댓글 + r/shopify 시도(rate limit)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>0 (프로필만)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>설정완료</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SEO Blog</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>6 포스트</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Show HN</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>미시작</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>DEV.to</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>미시작</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Shopify Community</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>미시작</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Product Hunt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>런치 완료 (3/27)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>대기중</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>최근 활동 로그</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-25 19:30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Division 로그 체계 구축 — D12 엑셀 + CLAUDE.md 규칙 + 매일 자동 점검 스케줄 설정 완료</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Cowork CW18 13차</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -773,6 +1186,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>내용</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>날짜</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-29 21:20 KST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>변경사항</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FreeBanner 제거 (app/page.tsx)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>이유</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>히어로 '140 Features. All Free. Forever.'와 중복 메시지</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>홈 화면 현재 상태</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>히어로에 무료 메시지 포함, 별도 배너 없음</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -875,7 +1366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1044,7 +1535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1175,7 +1666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1268,7 +1759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1368,7 +1859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1590,7 +2081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1694,295 +2185,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>채널</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>게시물수</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>팔로워/구독자</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>트래픽</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>마지막업데이트</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>PH 런치 포스트 + 첫 포스트 (2건)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>r/ecommerce 6댓글 + r/shopify 시도(rate limit)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>0 (프로필만)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>설정완료</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>SEO Blog</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>6 포스트</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>활성</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Show HN</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>미시작</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>DEV.to</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>미시작</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Shopify Community</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>미시작</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Product Hunt</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>런치 완료 (3/27)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>대기중</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>최근 활동 로그</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-25 19:30</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Division 로그 체계 구축 — D12 엑셀 + CLAUDE.md 규칙 + 매일 자동 점검 스케줄 설정 완료</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Cowork CW18 13차</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>